--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D0BB41-D6E3-46F7-A71D-D6DCCAEC4954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F11FFD-420F-418E-AFFC-AAB8E2885983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3382" yWindow="3008" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>StoryID</t>
   </si>
@@ -245,7 +234,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>若是这样，不如趁那小子不知情，便宜与了那小子….</t>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>若是这样，不如趁那小子不知情，便宜与了他去….</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -253,11 +246,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -271,7 +264,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -292,7 +285,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -427,7 +420,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -706,27 +699,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -776,7 +769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="16" t="s">
         <v>30</v>
       </c>
@@ -810,66 +803,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="C8" s="9"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -881,20 +874,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -920,7 +913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -942,7 +935,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -964,7 +957,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -984,7 +977,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1006,7 +999,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1026,7 +1019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1048,7 +1041,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1070,7 +1063,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1090,7 +1083,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1110,7 +1103,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1124,13 +1117,15 @@
         <v>47</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1150,7 +1145,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1168,7 +1163,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1188,7 +1183,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1208,7 +1203,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1228,7 +1223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1248,7 +1243,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1265,10 +1260,10 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F11FFD-420F-418E-AFFC-AAB8E2885983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D5DEF-8442-4D03-A5D0-8C9C72928373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3382" yWindow="3008" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="60">
   <si>
     <t>StoryID</t>
   </si>
@@ -57,10 +68,6 @@
   </si>
   <si>
     <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>right</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -166,14 +173,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>先生这是何意味？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>前些天你来看病，你前脚刚走，李公子就来我这问你的病情，很是担心你。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李郎待我是真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -182,10 +181,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>我有一计，可让你二人有情人终成眷属。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>sick</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -202,14 +197,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>少掌柜的你有什么注意呀？快说快说！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>明日你带金姨妈来我这，如此这般….</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>次日</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -238,7 +225,39 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>若是这样，不如趁那小子不知情，便宜与了他去….</t>
+    <t>(若是这样，不如趁那小子不知情，便宜与了他去….)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夫人这是何意味？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>前些天你来看病，你前脚刚走，李公子就来这问你的病情，很是担心你。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>我有一计，可使你二人有情人终成眷属。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少夫人你有什么注意呀？快说快说！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>明日你带让金姨妈来，如此这般….</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰和众人说出了自己的主意</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -246,11 +265,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -264,7 +283,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -285,7 +304,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -420,7 +439,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -699,96 +718,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="K1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="15" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -803,66 +822,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C8" s="9"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -873,21 +892,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -904,16 +923,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -921,21 +940,21 @@
         <v>7</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -943,21 +962,21 @@
         <v>7</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -965,19 +984,19 @@
         <v>7</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -985,21 +1004,21 @@
         <v>7</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1007,19 +1026,19 @@
         <v>7</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1027,21 +1046,21 @@
         <v>7</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1049,21 +1068,21 @@
         <v>7</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1071,207 +1090,223 @@
         <v>7</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>36</v>
+      <c r="C10" s="19" t="s">
+        <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>46</v>
+      <c r="C11" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>9</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="H14" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
+      <c r="C15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>51</v>
+      <c r="C16" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
+      <c r="C17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>51</v>
+      <c r="C18" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89D5DEF-8442-4D03-A5D0-8C9C72928373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4921AC3-3461-4E96-987E-C250683B606D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,10 +173,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李郎待我是真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>唉，我们这行当是做不长久的，只盼着有个如意的郎君，趁着年轻嫁入好人家。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -258,6 +254,10 @@
   </si>
   <si>
     <t>吴芷兰和众人说出了自己的主意</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -943,7 +943,7 @@
         <v>34</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
@@ -984,10 +984,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
@@ -1010,12 +1010,12 @@
         <v>9</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1026,16 +1026,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1052,12 +1052,12 @@
         <v>9</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1074,12 +1074,12 @@
         <v>9</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="19" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1090,16 +1090,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1110,18 +1110,18 @@
         <v>7</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1132,16 +1132,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>52</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1157,7 +1157,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1177,7 +1177,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1195,7 +1195,7 @@
         <v>28</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1206,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>9</v>
@@ -1215,7 +1215,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1229,13 +1229,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1246,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>9</v>
@@ -1255,7 +1255,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1269,13 +1269,13 @@
         <v>34</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1286,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>9</v>
@@ -1295,7 +1295,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4921AC3-3461-4E96-987E-C250683B606D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B00174-F537-457C-B54F-7E0E5F2A47D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,27 +237,27 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>前些天你来看病，你前脚刚走，李公子就来这问你的病情，很是担心你。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>我有一计，可使你二人有情人终成眷属。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>少夫人你有什么注意呀？快说快说！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>明日你带让金姨妈来，如此这般….</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>吴芷兰和众人说出了自己的主意</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>王郎待我真心诚意，我俩满心欢喜想着赎身之后拜堂成亲，可谁曾想干娘竟如此对我…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>前些天你来看病，你前脚刚走，王公子就来这问你的病情，很是担心你。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少夫人你有什么主意呀？快说快说！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>明日你让金姨妈来一趟，如此这般….</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1035,7 +1035,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1079,7 +1079,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1099,7 +1099,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1141,7 +1141,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1157,7 +1157,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B00174-F537-457C-B54F-7E0E5F2A47D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F7500-6479-4F13-83E2-17A5677D10DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="60">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="64">
   <si>
     <t>LineIndex</t>
   </si>
@@ -79,62 +65,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
@@ -146,9 +85,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>story_npc_cured</t>
-  </si>
-  <si>
     <t>024_01</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -259,17 +195,105 @@
   <si>
     <t>明日你让金姨妈来一趟，如此这般….</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>cured</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -283,7 +307,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -304,7 +328,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -319,13 +343,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,20 +378,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -384,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -407,24 +447,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -437,9 +466,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -717,175 +777,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultColWidth="19.46484375" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="22" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="22" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="M2" s="23"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="L3" s="17"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C8" s="9"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="13"/>
+      <c r="T2" s="25"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="12"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="8"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{0ABD7D92-F18A-449D-BCA3-CC6FA0298F23}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{F654C835-7EA3-4F8B-AD82-D73C9CD70AEE}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{59DB3D0A-ABF4-4DAE-BD6B-E09451D18A92}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{A0810F0C-911C-4459-84C3-6F8452F6C906}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{5F69A7C4-3FEE-4F03-9438-A0D2884D6965}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -893,412 +980,412 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H5" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H11" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="18"/>
+        <v>5</v>
+      </c>
+      <c r="C12" s="13"/>
       <c r="D12" s="7"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H12" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="2"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H15" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H16" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H17" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>34</v>
+        <v>6</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H18" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H19" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>

--- a/DataTables/DetailText/剧情/024_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/024_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F7500-6479-4F13-83E2-17A5677D10DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30364819-8445-4715-B88B-31B0B6D9A68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>LineIndex</t>
   </si>
@@ -284,6 +295,10 @@
   <si>
     <t>cured</t>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -293,7 +308,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -307,7 +322,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -328,7 +343,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -424,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -497,9 +512,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -778,25 +796,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="19.46484375" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="19.5" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>45</v>
       </c>
@@ -858,7 +876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1">
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
@@ -979,21 +997,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.375" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1018,8 +1036,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1040,8 +1061,9 @@
       <c r="H2" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1062,8 +1084,9 @@
       <c r="H3" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1082,8 +1105,9 @@
       <c r="H4" s="13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1104,8 +1128,9 @@
       <c r="H5" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1124,8 +1149,9 @@
       <c r="H6" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1146,8 +1172,9 @@
       <c r="H7" s="14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1168,8 +1195,9 @@
       <c r="H8" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1188,8 +1216,9 @@
       <c r="H9" s="14" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1210,8 +1239,9 @@
       <c r="H10" s="14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1230,8 +1260,9 @@
       <c r="H11" s="14" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1246,8 +1277,9 @@
       <c r="H12" s="14" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1266,8 +1298,9 @@
       <c r="H13" s="14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1284,8 +1317,9 @@
       <c r="H14" s="14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1304,8 +1338,9 @@
       <c r="H15" s="14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1324,8 +1359,9 @@
       <c r="H16" s="14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1344,8 +1380,9 @@
       <c r="H17" s="14" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1364,8 +1401,9 @@
       <c r="H18" s="14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1384,8 +1422,9 @@
       <c r="H19" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1394,6 +1433,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
+      <c r="I20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
